--- a/stories/arbres/ATOM-FAM.VER.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est dans la cuisine, près de maman. Maman coupe des pommes. Ça sent le fruit. Inès veut aider. Elle attrape le saladier. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Inès a le ventre serré. Elle va vers maman. Inès dit : maman, le saladier est tombé. J'ai fait tomber la farine. Maman s'approche. Maman dit : merci de raconter. On ramasse ensemble. Inès prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Papa entre. Inès dit : papa, j'ai raconté. Le saladier est tombé. Papa écoute. Papa dit : merci Inès. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>Inès est dans la cuisine, près de maman. Maman coupe des pommes. Ça sent le fruit. Inès veut aider. Elle attrape le saladier. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Inès a le ventre serré. Elle va vers maman. Maman, le saladier est tombé. J'ai fait tomber la farine. Maman s'approche. Merci de raconter. On ramasse ensemble. Inès prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Papa entre. Papa, j'ai raconté. Le saladier est tombé. Papa écoute. Merci Inès. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est dans la cuisine, près de maman. Maman coupe des pommes. Ça sent le fruit. Inès veut aider. Elle attrape le saladier. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Inès a le ventre serré. Elle va vers maman.
+enfant-f|Maman, le saladier est tombé. J'ai fait tomber la farine. Maman s'approche.
+maman|Merci de raconter. On ramasse ensemble.
+narrateur|Inès prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Papa entre.
+enfant-f|Papa, j'ai raconté.
+narrateur|Le saladier est tombé. Papa écoute.
+papa|Merci Inès. On raconte à papa ou maman. C'est comme ça.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La farine est tombée. Que fait Inès ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le sol est propre. Inès se lave les mains. Maman coupe encore une pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 papa|Merci Inès. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|La farine est tombée. Que fait Inès ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Inès a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Le sol est propre. Inès se lave les mains. Maman coupe encore une pomme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inès raconte à maman</t>
+          <t>Sarah raconte à maman</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut aider. Le saladier glisse. La farine tombe. Elle raconte à maman, puis à papa. Ils ramassent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est dans la cuisine, près de maman. Maman coupe des pommes. Ça sent le fruit. Inès veut aider. Elle attrape le saladier. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Inès a le ventre serré. Elle va vers maman. Maman, le saladier est tombé. J'ai fait tomber la farine. Maman s'approche. Merci de raconter. On ramasse ensemble. Inès prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Papa entre. Papa, j'ai raconté. Le saladier est tombé. Papa écoute. Merci Inès. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>La bouilloire chante tout bas. La vitre de la cuisine est embuée. Un doigt y a dessiné un cœur. Ça sent la cannelle. Des épluchures de pommes brillent. Elles sont rouges et un peu collantes. La cuillère en bois attend. Le saladier blanc est sur la table. Tu as vu le cœur sur la vitre, Sarah ? Oui, maman. Il est tout rond. Les pommes sentent bon. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Sarah tend les mains. Maman coupe encore une pomme. Sarah veut tenir le saladier. Elle l'attrape à deux mains. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Sarah a le ventre serré. Elle va vers maman. Maman, le saladier est tombé. J'ai fait tomber la farine. Je t'écoute, Sarah. Merci de raconter. On ramasse ensemble. Tu as fait du bon travail. Tu veux la petite balayette ? Oui, maman. Sarah prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Ça fait un bruit doux. Papa entre. Il pose un panier près de l'évier. Ça sent la cannelle, ici. Papa, j'ai raconté. Le saladier est tombé. La farine aussi. Je t'écoute. Merci Sarah. On raconte à papa ou maman. C'est comme ça. Bravo. Tu as su raconter. Le sol redevient propre, hein ? Oui, papa. Tu veux te laver les mains, maintenant ? Oui. L'eau est tiède. La farine part des doigts. Le ventre de Sarah se desserre. On coupe encore une pomme ? Oui. Une pomme rouge.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès est dans la cuisine, près de maman. Maman coupe des pommes. Ça sent le fruit. Inès veut aider. Elle attrape le saladier. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Inès a le ventre serré. Elle va vers maman.
-enfant-f|Maman, le saladier est tombé. J'ai fait tomber la farine. Maman s'approche.
-maman|Merci de raconter. On ramasse ensemble.
-narrateur|Inès prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Papa entre.
+          <t>narrateur|La bouilloire chante tout bas.
+narrateur|La vitre de la cuisine est embuée.
+narrateur|Un doigt y a dessiné un cœur.
+narrateur|Ça sent la cannelle.
+narrateur|Des épluchures de pommes brillent.
+narrateur|Elles sont rouges et un peu collantes.
+narrateur|La cuillère en bois attend.
+narrateur|Le saladier blanc est sur la table.
+maman|Tu as vu le cœur sur la vitre, Sarah ?
+enfant-f|Oui, maman.
+enfant-f|Il est tout rond.
+maman|Les pommes sentent bon.
+maman|Tu veux m'aider un peu ?
+enfant-f|Oui.
+enfant-f|Je veux aider.
+narrateur|En ce moment, Sarah tend les mains.
+narrateur|Maman coupe encore une pomme.
+narrateur|Sarah veut tenir le saladier.
+narrateur|Elle l'attrape à deux mains.
+narrateur|Le saladier glisse.
+narrateur|La farine tombe.
+narrateur|Ça fait un nuage blanc.
+narrateur|Le sol est blanc.
+narrateur|Sarah a le ventre serré.
+narrateur|Elle va vers maman.
+enfant-f|Maman, le saladier est tombé.
+enfant-f|J'ai fait tomber la farine.
+maman|Je t'écoute, Sarah.
+maman|Merci de raconter.
+maman|On ramasse ensemble.
+maman|Tu as fait du bon travail.
+maman|Tu veux la petite balayette ?
+enfant-f|Oui, maman.
+narrateur|Sarah prend la petite balayette.
+narrateur|Maman tient la pelle.
+narrateur|La farine revient dans le seau.
+narrateur|Ça fait un bruit doux.
+narrateur|Papa entre.
+narrateur|Il pose un panier près de l'évier.
+papa|Ça sent la cannelle, ici.
 enfant-f|Papa, j'ai raconté.
-narrateur|Le saladier est tombé. Papa écoute.
-papa|Merci Inès. On raconte à papa ou maman. C'est comme ça.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Le saladier est tombé.
+enfant-f|La farine aussi.
+papa|Je t'écoute.
+papa|Merci Sarah.
+papa|On raconte à papa ou maman.
+papa|C'est comme ça.
+papa|Bravo.
+papa|Tu as su raconter.
+papa|Le sol redevient propre, hein ?
+enfant-f|Oui, papa.
+maman|Tu veux te laver les mains, maintenant ?
+enfant-f|Oui.
+narrateur|L'eau est tiède.
+narrateur|La farine part des doigts.
+narrateur|Le ventre de Sarah se desserre.
+maman|On coupe encore une pomme ?
+enfant-f|Oui.
+enfant-f|Une pomme rouge.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>bouilloire,farine_tombe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La farine est tombée. Que fait Inès ?</t>
+          <t>La farine est tombée. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La farine est tombée. Que fait Inès ?</t>
+          <t>narrateur|La farine est tombée.
+narrateur|Que fait Sarah ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+          <t>Sarah a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Sarah. J'ai raconté. On a ramassé. Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1743,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+          <t>narrateur|Sarah a raconté.
+narrateur|Maman a écouté.
+narrateur|Papa a écouté.
+narrateur|Ensemble, ils ont ramassé.
+maman|Merci d'avoir raconté.
+papa|On raconte à papa ou maman.
+papa|Bravo, Sarah.
+enfant-f|J'ai raconté.
+enfant-f|On a ramassé.
+maman|Oui.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le sol est propre. Inès se lave les mains. Maman coupe encore une pomme.</t>
+          <t>Le sol est propre. Sarah se lave encore un doigt. Tu veux une rondelle de pomme ? Oui. Une rondelle. Elle est un peu sucrée. La bouilloire s'est tue. Le cœur sur la vitre reste. On reste un peu à table ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1921,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le sol est propre. Inès se lave les mains. Maman coupe encore une pomme.</t>
+          <t>narrateur|Le sol est propre.
+narrateur|Sarah se lave encore un doigt.
+maman|Tu veux une rondelle de pomme ?
+enfant-f|Oui.
+enfant-f|Une rondelle.
+papa|Elle est un peu sucrée.
+narrateur|La bouilloire s'est tue.
+narrateur|Le cœur sur la vitre reste.
+maman|On reste un peu à table ?
+enfant-f|Oui.
+enfant-f|Près de toi.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Maman a écouté. Bravo. Tu as fait du bon travail. Maman coupe encore une pomme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2099,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai raconté.
+enfant-f|Maman a écouté.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Maman coupe encore une pomme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante tout bas. La vitre de la cuisine est embuée. Un doigt y a dessiné un cœur. Ça sent la cannelle. Des épluchures de pommes brillent. Elles sont rouges et un peu collantes. La cuillère en bois attend. Le saladier blanc est sur la table. Tu as vu le cœur sur la vitre, Sarah ? Oui, maman. Il est tout rond. Les pommes sentent bon. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Sarah tend les mains. Maman coupe encore une pomme. Sarah veut tenir le saladier. Elle l'attrape à deux mains. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Sarah a le ventre serré. Elle va vers maman. Maman, le saladier est tombé. J'ai fait tomber la farine. Je t'écoute, Sarah. Merci de raconter. On ramasse ensemble. Tu as fait du bon travail. Tu veux la petite balayette ? Oui, maman. Sarah prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Ça fait un bruit doux. Papa entre. Il pose un panier près de l'évier. Ça sent la cannelle, ici. Papa, j'ai raconté. Le saladier est tombé. La farine aussi. Je t'écoute. Merci Sarah. On raconte à papa ou maman. C'est comme ça. Bravo. Tu as su raconter. Le sol redevient propre, hein ? Oui, papa. Tu veux te laver les mains, maintenant ? Oui. L'eau est tiède. La farine part des doigts. Le ventre de Sarah se desserre. On coupe encore une pomme ? Oui. Une pomme rouge.</t>
+          <t>La bouilloire chante tout bas. La vitre de la cuisine est embuée. Un doigt y a dessiné un cœur. Ça sent la cannelle. Des épluchures de pommes brillent. Elles sont rouges et un peu collantes. La cuillère en bois attend. Le saladier blanc est sur la table. Tu as vu le cœur sur la vitre, Sarah ? Oui, maman. Il est tout rond. Les pommes sentent bon. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Sarah tend les mains. Maman coupe encore une pomme. Sarah veut tenir le saladier. Elle l'attrape à deux mains. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Sarah a le ventre serré. Elle va vers maman. Maman, le saladier est tombé. J'ai fait tomber la farine. Je t'écoute, Sarah. Merci de raconter. On ramasse ensemble. Tu veux la petite balayette ? Oui, maman. Sarah prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Ça fait un bruit doux. Papa entre. Il pose un panier près de l'évier. Ça sent la cannelle, ici. Papa, j'ai raconté. Le saladier est tombé. La farine aussi. Je t'écoute. Merci Sarah. On raconte à papa ou maman. C'est comme ça. Bravo. Tu as su raconter. Le sol redevient propre, hein ? Oui, papa. Tu veux te laver les mains, maintenant ? Oui. L'eau est tiède. La farine part des doigts. Le ventre de Sarah se desserre. On coupe encore une pomme ? Oui. Une pomme rouge.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès est dans la cuisine, près de maman. Maman coupe des pommes. Ça sent le fruit. Inès veut aider. Elle attrape le saladier. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Inès a le ventre serré. Elle va vers maman. Inès dit : maman, le saladier est tombé. J'ai fait tomber la farine. Maman s'approche. Maman dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On ramasse ensemble. Inès prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Papa entre. Inès dit : papa, j'ai raconté. Le saladier est tombé. Papa écoute. Papa dit : merci Inès. On raconte à papa ou maman. C'est comme ça.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire chante tout bas. La vitre de la cuisine est embuée. Un doigt y a dessiné un cœur. Ça sent la cannelle. Des épluchures de pommes brillent. Elles sont rouges et un peu collantes. La cuillère en bois attend. Le saladier blanc est sur la table. Tu as vu le cœur sur la vitre, Sarah ? Oui, maman. Il est tout rond. Les pommes sentent bon. Tu veux m'aider un peu ? Oui. Je veux aider. En ce moment, Sarah tend les mains. Maman coupe encore une pomme. Sarah veut tenir le saladier. Elle l'attrape à deux mains. Le saladier glisse. La farine tombe. Ça fait un nuage blanc. Le sol est blanc. Sarah a le ventre serré. Elle va vers maman. Maman, le saladier est tombé. J'ai fait tomber la farine. Je t'écoute, Sarah. Merci de raconter. On ramasse ensemble. Tu veux la petite balayette ? Oui, maman. Sarah prend la petite balayette. Maman tient la pelle. La farine revient dans le seau. Ça fait un bruit doux. Papa entre. Il pose un panier près de l'évier. Ça sent la cannelle, ici. Papa, j'ai raconté. Le saladier est tombé. La farine aussi. Je t'écoute. Merci Sarah. On raconte à papa ou maman. C'est comme ça. Bravo. Tu as su raconter. Le sol redevient propre, hein ? Oui, papa. Tu veux te laver les mains, maintenant ? Oui. L'eau est tiède. La farine part des doigts. Le ventre de Sarah se desserre. On coupe encore une pomme ? Oui. Une pomme rouge.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1354,7 +1354,6 @@
 maman|Je t'écoute, Sarah.
 maman|Merci de raconter.
 maman|On ramasse ensemble.
-maman|Tu as fait du bon travail.
 maman|Tu veux la petite balayette ?
 enfant-f|Oui, maman.
 narrateur|Sarah prend la petite balayette.
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La farine est tombée. Que fait Inès ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La farine est tombée. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1573,6 @@
 narrateur|Que fait Sarah ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Sarah. J'ai raconté. On a ramassé. Oui. C'est du bon travail.</t>
+          <t>Sarah a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Sarah. J'ai raconté. On a ramassé. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt; aide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a raconté. Maman a écouté. Papa a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Sarah. J'ai raconté. On a ramassé. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,11 +1750,9 @@
 papa|Bravo, Sarah.
 enfant-f|J'ai raconté.
 enfant-f|On a ramassé.
-maman|Oui.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le sol est propre. Inès se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Maman coupe encore une pomme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sol est propre. Sarah se lave encore un doigt. Tu veux une rondelle de pomme ? Oui. Une rondelle. Elle est un peu sucrée. La bouilloire s'est tue. Le cœur sur la vitre reste. On reste un peu à table ? Oui. Près de toi.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,7 +1930,6 @@
 enfant-f|Près de toi.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Maman a écouté. Bravo. Tu as fait du bon travail. Maman coupe encore une pomme. L'histoire est finie.</t>
+          <t>J'ai raconté. Maman a écouté. Bravo. Maman coupe encore une pomme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Maman a écouté. Bravo. Maman coupe encore une pomme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,12 +2097,9 @@
           <t>enfant-f|J'ai raconté.
 enfant-f|Maman a écouté.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Maman coupe encore une pomme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Maman coupe encore une pomme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2126,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-01.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, maman, papa</t>
+          <t>Sarah, maman, papa</t>
         </is>
       </c>
     </row>
